--- a/proje/hesaplar_sema/HESAPLAR_SIHHI.xlsx
+++ b/proje/hesaplar_sema/HESAPLAR_SIHHI.xlsx
@@ -11,9 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1 BLOK" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2 BLOK" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B3 BLOK" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ÇİZELGE_1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ÇİZELGE_2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ÇİZELGE_3" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PİS SU POMPALARI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HİDROFOR-DEPO" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ÇİZELGE_1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ÇİZELGE_2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ÇİZELGE_3" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +499,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Statik kot farkı = 7 kat x 3.00 m + 1.50 m armatür yüksekliği = 22.50 m  →  220658 Pa</t>
+          <t>Statik kot farkı (bina yüksekliği) = 21.00 m  →  205947 Pa</t>
         </is>
       </c>
     </row>
@@ -511,14 +513,14 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ETKİN BASINÇ = 67.10x9807-(22.50x9807+49035+49035) = 339322 Pa</t>
+          <t>ETKİN BASINÇ = 67.10x9807-(21.00x9807+49035+49035) = 354033 Pa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ORTALAMA ÖZGÜL BASINÇ KAYBI = Etkin basınç / Kritik devre uzunluğu = 339322/97 = 3498 Pa/m</t>
+          <t>ORTALAMA ÖZGÜL BASINÇ KAYBI = Etkin basınç / Kritik devre uzunluğu = 354033/97 = 3650 Pa/m</t>
         </is>
       </c>
     </row>
@@ -917,7 +919,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <f>IF(G21&lt;339322,TEXT(G21,"0")&amp;" &lt; 339322 Pa OLDUĞUNDAN UYGUNDUR.",TEXT(G21,"0")&amp;" &gt; 339322 Pa - ÇAPLAR BÜYÜTÜLMELİDİR.")</f>
+        <f>IF(G21&lt;354033,TEXT(G21,"0")&amp;" &lt; 354033 Pa OLDUĞUNDAN UYGUNDUR.",TEXT(G21,"0")&amp;" &gt; 354033 Pa - ÇAPLAR BÜYÜTÜLMELİDİR.")</f>
         <v/>
       </c>
     </row>
@@ -945,7 +947,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>*Boru YB ve çap değerleri şemadaki MTY çap etiketlerinden alınmıştır; kat yüksekliği 3,00 m kabul edilmiştir.</t>
+          <t>*Boru YB ve çap değerleri şemadaki MTY çap etiketlerinden alınmıştır; bina yüksekliği 21 m (kat başı 3,00 m) alınmıştır.</t>
         </is>
       </c>
     </row>
@@ -967,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M46"/>
+  <dimension ref="B1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1558,161 +1560,139 @@
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="1" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>IZGARA (Ø100)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="4">
+        <f>SUM(D24:L24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>PİS SU - KOLON YÜKLERİ (SB)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>CİNSİ</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>YÜK (SB)</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
-      </c>
-      <c r="M27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>KLOZET,HELA</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D28" s="4">
-        <f>$C28*N(D16)</f>
-        <v/>
-      </c>
-      <c r="E28" s="4">
-        <f>$C28*N(E16)</f>
-        <v/>
-      </c>
-      <c r="F28" s="4">
-        <f>$C28*N(F16)</f>
-        <v/>
-      </c>
-      <c r="G28" s="4">
-        <f>$C28*N(G16)</f>
-        <v/>
-      </c>
-      <c r="H28" s="4">
-        <f>$C28*N(H16)</f>
-        <v/>
-      </c>
-      <c r="I28" s="4">
-        <f>$C28*N(I16)</f>
-        <v/>
-      </c>
-      <c r="J28" s="4">
-        <f>$C28*N(J16)</f>
-        <v/>
-      </c>
-      <c r="K28" s="4">
-        <f>$C28*N(K16)</f>
-        <v/>
-      </c>
-      <c r="L28" s="4">
-        <f>$C28*N(L16)</f>
-        <v/>
       </c>
       <c r="M28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>BANYO KÜVETİ-DUŞ</t>
+          <t>KLOZET,HELA</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D29" s="4">
-        <f>$C29*N(D17)</f>
+        <f>$C29*N(D16)</f>
         <v/>
       </c>
       <c r="E29" s="4">
-        <f>$C29*N(E17)</f>
+        <f>$C29*N(E16)</f>
         <v/>
       </c>
       <c r="F29" s="4">
-        <f>$C29*N(F17)</f>
+        <f>$C29*N(F16)</f>
         <v/>
       </c>
       <c r="G29" s="4">
-        <f>$C29*N(G17)</f>
+        <f>$C29*N(G16)</f>
         <v/>
       </c>
       <c r="H29" s="4">
-        <f>$C29*N(H17)</f>
+        <f>$C29*N(H16)</f>
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>$C29*N(I17)</f>
+        <f>$C29*N(I16)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>$C29*N(J17)</f>
+        <f>$C29*N(J16)</f>
         <v/>
       </c>
       <c r="K29" s="4">
-        <f>$C29*N(K17)</f>
+        <f>$C29*N(K16)</f>
         <v/>
       </c>
       <c r="L29" s="4">
-        <f>$C29*N(L17)</f>
+        <f>$C29*N(L16)</f>
         <v/>
       </c>
       <c r="M29" s="4" t="n"/>
@@ -1720,46 +1700,46 @@
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>SİFON,EVİYE</t>
+          <t>BANYO KÜVETİ-DUŞ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D30" s="4">
-        <f>$C30*N(D18)</f>
+        <f>$C30*N(D17)</f>
         <v/>
       </c>
       <c r="E30" s="4">
-        <f>$C30*N(E18)</f>
+        <f>$C30*N(E17)</f>
         <v/>
       </c>
       <c r="F30" s="4">
-        <f>$C30*N(F18)</f>
+        <f>$C30*N(F17)</f>
         <v/>
       </c>
       <c r="G30" s="4">
-        <f>$C30*N(G18)</f>
+        <f>$C30*N(G17)</f>
         <v/>
       </c>
       <c r="H30" s="4">
-        <f>$C30*N(H18)</f>
+        <f>$C30*N(H17)</f>
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>$C30*N(I18)</f>
+        <f>$C30*N(I17)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>$C30*N(J18)</f>
+        <f>$C30*N(J17)</f>
         <v/>
       </c>
       <c r="K30" s="4">
-        <f>$C30*N(K18)</f>
+        <f>$C30*N(K17)</f>
         <v/>
       </c>
       <c r="L30" s="4">
-        <f>$C30*N(L18)</f>
+        <f>$C30*N(L17)</f>
         <v/>
       </c>
       <c r="M30" s="4" t="n"/>
@@ -1767,46 +1747,46 @@
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>İKİ GÖZLÜ EVİYE</t>
+          <t>SİFON,EVİYE</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D31" s="4">
-        <f>$C31*N(D19)</f>
+        <f>$C31*N(D18)</f>
         <v/>
       </c>
       <c r="E31" s="4">
-        <f>$C31*N(E19)</f>
+        <f>$C31*N(E18)</f>
         <v/>
       </c>
       <c r="F31" s="4">
-        <f>$C31*N(F19)</f>
+        <f>$C31*N(F18)</f>
         <v/>
       </c>
       <c r="G31" s="4">
-        <f>$C31*N(G19)</f>
+        <f>$C31*N(G18)</f>
         <v/>
       </c>
       <c r="H31" s="4">
-        <f>$C31*N(H19)</f>
+        <f>$C31*N(H18)</f>
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>$C31*N(I19)</f>
+        <f>$C31*N(I18)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>$C31*N(J19)</f>
+        <f>$C31*N(J18)</f>
         <v/>
       </c>
       <c r="K31" s="4">
-        <f>$C31*N(K19)</f>
+        <f>$C31*N(K18)</f>
         <v/>
       </c>
       <c r="L31" s="4">
-        <f>$C31*N(L19)</f>
+        <f>$C31*N(L18)</f>
         <v/>
       </c>
       <c r="M31" s="4" t="n"/>
@@ -1814,46 +1794,46 @@
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>LAVABO</t>
+          <t>İKİ GÖZLÜ EVİYE</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D32" s="4">
-        <f>$C32*N(D20)</f>
+        <f>$C32*N(D19)</f>
         <v/>
       </c>
       <c r="E32" s="4">
-        <f>$C32*N(E20)</f>
+        <f>$C32*N(E19)</f>
         <v/>
       </c>
       <c r="F32" s="4">
-        <f>$C32*N(F20)</f>
+        <f>$C32*N(F19)</f>
         <v/>
       </c>
       <c r="G32" s="4">
-        <f>$C32*N(G20)</f>
+        <f>$C32*N(G19)</f>
         <v/>
       </c>
       <c r="H32" s="4">
-        <f>$C32*N(H20)</f>
+        <f>$C32*N(H19)</f>
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>$C32*N(I20)</f>
+        <f>$C32*N(I19)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>$C32*N(J20)</f>
+        <f>$C32*N(J19)</f>
         <v/>
       </c>
       <c r="K32" s="4">
-        <f>$C32*N(K20)</f>
+        <f>$C32*N(K19)</f>
         <v/>
       </c>
       <c r="L32" s="4">
-        <f>$C32*N(L20)</f>
+        <f>$C32*N(L19)</f>
         <v/>
       </c>
       <c r="M32" s="4" t="n"/>
@@ -1861,46 +1841,46 @@
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>YERSÜZGECİ</t>
+          <t>LAVABO</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="4">
-        <f>$C33*N(D21)</f>
+        <f>$C33*N(D20)</f>
         <v/>
       </c>
       <c r="E33" s="4">
-        <f>$C33*N(E21)</f>
+        <f>$C33*N(E20)</f>
         <v/>
       </c>
       <c r="F33" s="4">
-        <f>$C33*N(F21)</f>
+        <f>$C33*N(F20)</f>
         <v/>
       </c>
       <c r="G33" s="4">
-        <f>$C33*N(G21)</f>
+        <f>$C33*N(G20)</f>
         <v/>
       </c>
       <c r="H33" s="4">
-        <f>$C33*N(H21)</f>
+        <f>$C33*N(H20)</f>
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>$C33*N(I21)</f>
+        <f>$C33*N(I20)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>$C33*N(J21)</f>
+        <f>$C33*N(J20)</f>
         <v/>
       </c>
       <c r="K33" s="4">
-        <f>$C33*N(K21)</f>
+        <f>$C33*N(K20)</f>
         <v/>
       </c>
       <c r="L33" s="4">
-        <f>$C33*N(L21)</f>
+        <f>$C33*N(L20)</f>
         <v/>
       </c>
       <c r="M33" s="4" t="n"/>
@@ -1908,46 +1888,46 @@
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ÇAMAŞIR,BUL.MAK</t>
+          <t>YERSÜZGECİ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34" s="4">
-        <f>$C34*N(D22)</f>
+        <f>$C34*N(D21)</f>
         <v/>
       </c>
       <c r="E34" s="4">
-        <f>$C34*N(E22)</f>
+        <f>$C34*N(E21)</f>
         <v/>
       </c>
       <c r="F34" s="4">
-        <f>$C34*N(F22)</f>
+        <f>$C34*N(F21)</f>
         <v/>
       </c>
       <c r="G34" s="4">
-        <f>$C34*N(G22)</f>
+        <f>$C34*N(G21)</f>
         <v/>
       </c>
       <c r="H34" s="4">
-        <f>$C34*N(H22)</f>
+        <f>$C34*N(H21)</f>
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>$C34*N(I22)</f>
+        <f>$C34*N(I21)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>$C34*N(J22)</f>
+        <f>$C34*N(J21)</f>
         <v/>
       </c>
       <c r="K34" s="4">
-        <f>$C34*N(K22)</f>
+        <f>$C34*N(K21)</f>
         <v/>
       </c>
       <c r="L34" s="4">
-        <f>$C34*N(L22)</f>
+        <f>$C34*N(L21)</f>
         <v/>
       </c>
       <c r="M34" s="4" t="n"/>
@@ -1955,223 +1935,317 @@
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>ÇAMAŞIR,BUL.MAK</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="4">
+        <f>$C35*N(D22)</f>
+        <v/>
+      </c>
+      <c r="E35" s="4">
+        <f>$C35*N(E22)</f>
+        <v/>
+      </c>
+      <c r="F35" s="4">
+        <f>$C35*N(F22)</f>
+        <v/>
+      </c>
+      <c r="G35" s="4">
+        <f>$C35*N(G22)</f>
+        <v/>
+      </c>
+      <c r="H35" s="4">
+        <f>$C35*N(H22)</f>
+        <v/>
+      </c>
+      <c r="I35" s="4">
+        <f>$C35*N(I22)</f>
+        <v/>
+      </c>
+      <c r="J35" s="4">
+        <f>$C35*N(J22)</f>
+        <v/>
+      </c>
+      <c r="K35" s="4">
+        <f>$C35*N(K22)</f>
+        <v/>
+      </c>
+      <c r="L35" s="4">
+        <f>$C35*N(L22)</f>
+        <v/>
+      </c>
+      <c r="M35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>PİSUVAR</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C36" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="4">
-        <f>$C35*N(D23)</f>
-        <v/>
-      </c>
-      <c r="E35" s="4">
-        <f>$C35*N(E23)</f>
-        <v/>
-      </c>
-      <c r="F35" s="4">
-        <f>$C35*N(F23)</f>
-        <v/>
-      </c>
-      <c r="G35" s="4">
-        <f>$C35*N(G23)</f>
-        <v/>
-      </c>
-      <c r="H35" s="4">
-        <f>$C35*N(H23)</f>
-        <v/>
-      </c>
-      <c r="I35" s="4">
-        <f>$C35*N(I23)</f>
-        <v/>
-      </c>
-      <c r="J35" s="4">
-        <f>$C35*N(J23)</f>
-        <v/>
-      </c>
-      <c r="K35" s="4">
-        <f>$C35*N(K23)</f>
-        <v/>
-      </c>
-      <c r="L35" s="4">
-        <f>$C35*N(L23)</f>
-        <v/>
-      </c>
-      <c r="M35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>TOPLAM</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="6">
-        <f>SUM(D28:D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="6">
-        <f>SUM(E28:E35)</f>
-        <v/>
-      </c>
-      <c r="F36" s="6">
-        <f>SUM(F28:F35)</f>
-        <v/>
-      </c>
-      <c r="G36" s="6">
-        <f>SUM(G28:G35)</f>
-        <v/>
-      </c>
-      <c r="H36" s="6">
-        <f>SUM(H28:H35)</f>
-        <v/>
-      </c>
-      <c r="I36" s="6">
-        <f>SUM(I28:I35)</f>
-        <v/>
-      </c>
-      <c r="J36" s="6">
-        <f>SUM(J28:J35)</f>
-        <v/>
-      </c>
-      <c r="K36" s="6">
-        <f>SUM(K28:K35)</f>
-        <v/>
-      </c>
-      <c r="L36" s="6">
-        <f>SUM(L28:L35)</f>
-        <v/>
-      </c>
-      <c r="M36" s="6">
-        <f>SUM(D36:L36)</f>
-        <v/>
-      </c>
+      <c r="D36" s="4">
+        <f>$C36*N(D23)</f>
+        <v/>
+      </c>
+      <c r="E36" s="4">
+        <f>$C36*N(E23)</f>
+        <v/>
+      </c>
+      <c r="F36" s="4">
+        <f>$C36*N(F23)</f>
+        <v/>
+      </c>
+      <c r="G36" s="4">
+        <f>$C36*N(G23)</f>
+        <v/>
+      </c>
+      <c r="H36" s="4">
+        <f>$C36*N(H23)</f>
+        <v/>
+      </c>
+      <c r="I36" s="4">
+        <f>$C36*N(I23)</f>
+        <v/>
+      </c>
+      <c r="J36" s="4">
+        <f>$C36*N(J23)</f>
+        <v/>
+      </c>
+      <c r="K36" s="4">
+        <f>$C36*N(K23)</f>
+        <v/>
+      </c>
+      <c r="L36" s="4">
+        <f>$C36*N(L23)</f>
+        <v/>
+      </c>
+      <c r="M36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>IZGARA (Ø100)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="4">
+        <f>$C37*N(D24)</f>
+        <v/>
+      </c>
+      <c r="E37" s="4">
+        <f>$C37*N(E24)</f>
+        <v/>
+      </c>
+      <c r="F37" s="4">
+        <f>$C37*N(F24)</f>
+        <v/>
+      </c>
+      <c r="G37" s="4">
+        <f>$C37*N(G24)</f>
+        <v/>
+      </c>
+      <c r="H37" s="4">
+        <f>$C37*N(H24)</f>
+        <v/>
+      </c>
+      <c r="I37" s="4">
+        <f>$C37*N(I24)</f>
+        <v/>
+      </c>
+      <c r="J37" s="4">
+        <f>$C37*N(J24)</f>
+        <v/>
+      </c>
+      <c r="K37" s="4">
+        <f>$C37*N(K24)</f>
+        <v/>
+      </c>
+      <c r="L37" s="4">
+        <f>$C37*N(L24)</f>
+        <v/>
+      </c>
+      <c r="M37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="6">
+        <f>SUM(D29:D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="6">
+        <f>SUM(E29:E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="6">
+        <f>SUM(F29:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="6">
+        <f>SUM(G29:G37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="6">
+        <f>SUM(H29:H37)</f>
+        <v/>
+      </c>
+      <c r="I38" s="6">
+        <f>SUM(I29:I37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="6">
+        <f>SUM(J29:J37)</f>
+        <v/>
+      </c>
+      <c r="K38" s="6">
+        <f>SUM(K29:K37)</f>
+        <v/>
+      </c>
+      <c r="L38" s="6">
+        <f>SUM(L29:L37)</f>
+        <v/>
+      </c>
+      <c r="M38" s="6">
+        <f>SUM(D38:L38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
           <t>Qww = 0,5 x √ΣSB (l/s)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4">
-        <f>ROUND(0.5*SQRT(D36),2)</f>
-        <v/>
-      </c>
-      <c r="E37" s="4">
-        <f>ROUND(0.5*SQRT(E36),2)</f>
-        <v/>
-      </c>
-      <c r="F37" s="4">
-        <f>ROUND(0.5*SQRT(F36),2)</f>
-        <v/>
-      </c>
-      <c r="G37" s="4">
-        <f>ROUND(0.5*SQRT(G36),2)</f>
-        <v/>
-      </c>
-      <c r="H37" s="4">
-        <f>ROUND(0.5*SQRT(H36),2)</f>
-        <v/>
-      </c>
-      <c r="I37" s="4">
-        <f>ROUND(0.5*SQRT(I36),2)</f>
-        <v/>
-      </c>
-      <c r="J37" s="4">
-        <f>ROUND(0.5*SQRT(J36),2)</f>
-        <v/>
-      </c>
-      <c r="K37" s="4">
-        <f>ROUND(0.5*SQRT(K36),2)</f>
-        <v/>
-      </c>
-      <c r="L37" s="4">
-        <f>ROUND(0.5*SQRT(L36),2)</f>
-        <v/>
-      </c>
-      <c r="M37" s="4" t="n"/>
-    </row>
-    <row r="40">
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4">
+        <f>ROUND(0.5*SQRT(D38),2)</f>
+        <v/>
+      </c>
+      <c r="E39" s="4">
+        <f>ROUND(0.5*SQRT(E38),2)</f>
+        <v/>
+      </c>
+      <c r="F39" s="4">
+        <f>ROUND(0.5*SQRT(F38),2)</f>
+        <v/>
+      </c>
+      <c r="G39" s="4">
+        <f>ROUND(0.5*SQRT(G38),2)</f>
+        <v/>
+      </c>
+      <c r="H39" s="4">
+        <f>ROUND(0.5*SQRT(H38),2)</f>
+        <v/>
+      </c>
+      <c r="I39" s="4">
+        <f>ROUND(0.5*SQRT(I38),2)</f>
+        <v/>
+      </c>
+      <c r="J39" s="4">
+        <f>ROUND(0.5*SQRT(J38),2)</f>
+        <v/>
+      </c>
+      <c r="K39" s="4">
+        <f>ROUND(0.5*SQRT(K38),2)</f>
+        <v/>
+      </c>
+      <c r="L39" s="4">
+        <f>ROUND(0.5*SQRT(L38),2)</f>
+        <v/>
+      </c>
+      <c r="M39" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>BORU ÇAPI</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>K.B.</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>YÜK DEĞERİ</t>
         </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="C43" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="C44" s="4" t="n">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>270</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="C45" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D45" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="D45" s="4" t="n">
-        <v>900</v>
-      </c>
       <c r="E45" s="4" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="C46" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D48" s="4" t="n">
         <v>2200</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E48" s="4" t="n">
         <v>1550</v>
       </c>
     </row>
@@ -2186,7 +2260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O46"/>
+  <dimension ref="B1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2821,187 +2895,157 @@
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="1" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>IZGARA (Ø100)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4">
+        <f>SUM(D24:N24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>PİS SU - KOLON YÜKLERİ (SB)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>CİNSİ</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>YÜK (SB)</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
-      </c>
-      <c r="O27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>KLOZET,HELA</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D28" s="4">
-        <f>$C28*N(D16)</f>
-        <v/>
-      </c>
-      <c r="E28" s="4">
-        <f>$C28*N(E16)</f>
-        <v/>
-      </c>
-      <c r="F28" s="4">
-        <f>$C28*N(F16)</f>
-        <v/>
-      </c>
-      <c r="G28" s="4">
-        <f>$C28*N(G16)</f>
-        <v/>
-      </c>
-      <c r="H28" s="4">
-        <f>$C28*N(H16)</f>
-        <v/>
-      </c>
-      <c r="I28" s="4">
-        <f>$C28*N(I16)</f>
-        <v/>
-      </c>
-      <c r="J28" s="4">
-        <f>$C28*N(J16)</f>
-        <v/>
-      </c>
-      <c r="K28" s="4">
-        <f>$C28*N(K16)</f>
-        <v/>
-      </c>
-      <c r="L28" s="4">
-        <f>$C28*N(L16)</f>
-        <v/>
-      </c>
-      <c r="M28" s="4">
-        <f>$C28*N(M16)</f>
-        <v/>
-      </c>
-      <c r="N28" s="4">
-        <f>$C28*N(N16)</f>
-        <v/>
       </c>
       <c r="O28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>BANYO KÜVETİ-DUŞ</t>
+          <t>KLOZET,HELA</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D29" s="4">
-        <f>$C29*N(D17)</f>
+        <f>$C29*N(D16)</f>
         <v/>
       </c>
       <c r="E29" s="4">
-        <f>$C29*N(E17)</f>
+        <f>$C29*N(E16)</f>
         <v/>
       </c>
       <c r="F29" s="4">
-        <f>$C29*N(F17)</f>
+        <f>$C29*N(F16)</f>
         <v/>
       </c>
       <c r="G29" s="4">
-        <f>$C29*N(G17)</f>
+        <f>$C29*N(G16)</f>
         <v/>
       </c>
       <c r="H29" s="4">
-        <f>$C29*N(H17)</f>
+        <f>$C29*N(H16)</f>
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>$C29*N(I17)</f>
+        <f>$C29*N(I16)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>$C29*N(J17)</f>
+        <f>$C29*N(J16)</f>
         <v/>
       </c>
       <c r="K29" s="4">
-        <f>$C29*N(K17)</f>
+        <f>$C29*N(K16)</f>
         <v/>
       </c>
       <c r="L29" s="4">
-        <f>$C29*N(L17)</f>
+        <f>$C29*N(L16)</f>
         <v/>
       </c>
       <c r="M29" s="4">
-        <f>$C29*N(M17)</f>
+        <f>$C29*N(M16)</f>
         <v/>
       </c>
       <c r="N29" s="4">
-        <f>$C29*N(N17)</f>
+        <f>$C29*N(N16)</f>
         <v/>
       </c>
       <c r="O29" s="4" t="n"/>
@@ -3009,54 +3053,54 @@
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>SİFON,EVİYE</t>
+          <t>BANYO KÜVETİ-DUŞ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D30" s="4">
-        <f>$C30*N(D18)</f>
+        <f>$C30*N(D17)</f>
         <v/>
       </c>
       <c r="E30" s="4">
-        <f>$C30*N(E18)</f>
+        <f>$C30*N(E17)</f>
         <v/>
       </c>
       <c r="F30" s="4">
-        <f>$C30*N(F18)</f>
+        <f>$C30*N(F17)</f>
         <v/>
       </c>
       <c r="G30" s="4">
-        <f>$C30*N(G18)</f>
+        <f>$C30*N(G17)</f>
         <v/>
       </c>
       <c r="H30" s="4">
-        <f>$C30*N(H18)</f>
+        <f>$C30*N(H17)</f>
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>$C30*N(I18)</f>
+        <f>$C30*N(I17)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>$C30*N(J18)</f>
+        <f>$C30*N(J17)</f>
         <v/>
       </c>
       <c r="K30" s="4">
-        <f>$C30*N(K18)</f>
+        <f>$C30*N(K17)</f>
         <v/>
       </c>
       <c r="L30" s="4">
-        <f>$C30*N(L18)</f>
+        <f>$C30*N(L17)</f>
         <v/>
       </c>
       <c r="M30" s="4">
-        <f>$C30*N(M18)</f>
+        <f>$C30*N(M17)</f>
         <v/>
       </c>
       <c r="N30" s="4">
-        <f>$C30*N(N18)</f>
+        <f>$C30*N(N17)</f>
         <v/>
       </c>
       <c r="O30" s="4" t="n"/>
@@ -3064,54 +3108,54 @@
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>İKİ GÖZLÜ EVİYE</t>
+          <t>SİFON,EVİYE</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D31" s="4">
-        <f>$C31*N(D19)</f>
+        <f>$C31*N(D18)</f>
         <v/>
       </c>
       <c r="E31" s="4">
-        <f>$C31*N(E19)</f>
+        <f>$C31*N(E18)</f>
         <v/>
       </c>
       <c r="F31" s="4">
-        <f>$C31*N(F19)</f>
+        <f>$C31*N(F18)</f>
         <v/>
       </c>
       <c r="G31" s="4">
-        <f>$C31*N(G19)</f>
+        <f>$C31*N(G18)</f>
         <v/>
       </c>
       <c r="H31" s="4">
-        <f>$C31*N(H19)</f>
+        <f>$C31*N(H18)</f>
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>$C31*N(I19)</f>
+        <f>$C31*N(I18)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>$C31*N(J19)</f>
+        <f>$C31*N(J18)</f>
         <v/>
       </c>
       <c r="K31" s="4">
-        <f>$C31*N(K19)</f>
+        <f>$C31*N(K18)</f>
         <v/>
       </c>
       <c r="L31" s="4">
-        <f>$C31*N(L19)</f>
+        <f>$C31*N(L18)</f>
         <v/>
       </c>
       <c r="M31" s="4">
-        <f>$C31*N(M19)</f>
+        <f>$C31*N(M18)</f>
         <v/>
       </c>
       <c r="N31" s="4">
-        <f>$C31*N(N19)</f>
+        <f>$C31*N(N18)</f>
         <v/>
       </c>
       <c r="O31" s="4" t="n"/>
@@ -3119,54 +3163,54 @@
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>LAVABO</t>
+          <t>İKİ GÖZLÜ EVİYE</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D32" s="4">
-        <f>$C32*N(D20)</f>
+        <f>$C32*N(D19)</f>
         <v/>
       </c>
       <c r="E32" s="4">
-        <f>$C32*N(E20)</f>
+        <f>$C32*N(E19)</f>
         <v/>
       </c>
       <c r="F32" s="4">
-        <f>$C32*N(F20)</f>
+        <f>$C32*N(F19)</f>
         <v/>
       </c>
       <c r="G32" s="4">
-        <f>$C32*N(G20)</f>
+        <f>$C32*N(G19)</f>
         <v/>
       </c>
       <c r="H32" s="4">
-        <f>$C32*N(H20)</f>
+        <f>$C32*N(H19)</f>
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>$C32*N(I20)</f>
+        <f>$C32*N(I19)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>$C32*N(J20)</f>
+        <f>$C32*N(J19)</f>
         <v/>
       </c>
       <c r="K32" s="4">
-        <f>$C32*N(K20)</f>
+        <f>$C32*N(K19)</f>
         <v/>
       </c>
       <c r="L32" s="4">
-        <f>$C32*N(L20)</f>
+        <f>$C32*N(L19)</f>
         <v/>
       </c>
       <c r="M32" s="4">
-        <f>$C32*N(M20)</f>
+        <f>$C32*N(M19)</f>
         <v/>
       </c>
       <c r="N32" s="4">
-        <f>$C32*N(N20)</f>
+        <f>$C32*N(N19)</f>
         <v/>
       </c>
       <c r="O32" s="4" t="n"/>
@@ -3174,54 +3218,54 @@
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>YERSÜZGECİ</t>
+          <t>LAVABO</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="4">
-        <f>$C33*N(D21)</f>
+        <f>$C33*N(D20)</f>
         <v/>
       </c>
       <c r="E33" s="4">
-        <f>$C33*N(E21)</f>
+        <f>$C33*N(E20)</f>
         <v/>
       </c>
       <c r="F33" s="4">
-        <f>$C33*N(F21)</f>
+        <f>$C33*N(F20)</f>
         <v/>
       </c>
       <c r="G33" s="4">
-        <f>$C33*N(G21)</f>
+        <f>$C33*N(G20)</f>
         <v/>
       </c>
       <c r="H33" s="4">
-        <f>$C33*N(H21)</f>
+        <f>$C33*N(H20)</f>
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>$C33*N(I21)</f>
+        <f>$C33*N(I20)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>$C33*N(J21)</f>
+        <f>$C33*N(J20)</f>
         <v/>
       </c>
       <c r="K33" s="4">
-        <f>$C33*N(K21)</f>
+        <f>$C33*N(K20)</f>
         <v/>
       </c>
       <c r="L33" s="4">
-        <f>$C33*N(L21)</f>
+        <f>$C33*N(L20)</f>
         <v/>
       </c>
       <c r="M33" s="4">
-        <f>$C33*N(M21)</f>
+        <f>$C33*N(M20)</f>
         <v/>
       </c>
       <c r="N33" s="4">
-        <f>$C33*N(N21)</f>
+        <f>$C33*N(N20)</f>
         <v/>
       </c>
       <c r="O33" s="4" t="n"/>
@@ -3229,54 +3273,54 @@
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ÇAMAŞIR,BUL.MAK</t>
+          <t>YERSÜZGECİ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34" s="4">
-        <f>$C34*N(D22)</f>
+        <f>$C34*N(D21)</f>
         <v/>
       </c>
       <c r="E34" s="4">
-        <f>$C34*N(E22)</f>
+        <f>$C34*N(E21)</f>
         <v/>
       </c>
       <c r="F34" s="4">
-        <f>$C34*N(F22)</f>
+        <f>$C34*N(F21)</f>
         <v/>
       </c>
       <c r="G34" s="4">
-        <f>$C34*N(G22)</f>
+        <f>$C34*N(G21)</f>
         <v/>
       </c>
       <c r="H34" s="4">
-        <f>$C34*N(H22)</f>
+        <f>$C34*N(H21)</f>
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>$C34*N(I22)</f>
+        <f>$C34*N(I21)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>$C34*N(J22)</f>
+        <f>$C34*N(J21)</f>
         <v/>
       </c>
       <c r="K34" s="4">
-        <f>$C34*N(K22)</f>
+        <f>$C34*N(K21)</f>
         <v/>
       </c>
       <c r="L34" s="4">
-        <f>$C34*N(L22)</f>
+        <f>$C34*N(L21)</f>
         <v/>
       </c>
       <c r="M34" s="4">
-        <f>$C34*N(M22)</f>
+        <f>$C34*N(M21)</f>
         <v/>
       </c>
       <c r="N34" s="4">
-        <f>$C34*N(N22)</f>
+        <f>$C34*N(N21)</f>
         <v/>
       </c>
       <c r="O34" s="4" t="n"/>
@@ -3284,247 +3328,357 @@
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>ÇAMAŞIR,BUL.MAK</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="4">
+        <f>$C35*N(D22)</f>
+        <v/>
+      </c>
+      <c r="E35" s="4">
+        <f>$C35*N(E22)</f>
+        <v/>
+      </c>
+      <c r="F35" s="4">
+        <f>$C35*N(F22)</f>
+        <v/>
+      </c>
+      <c r="G35" s="4">
+        <f>$C35*N(G22)</f>
+        <v/>
+      </c>
+      <c r="H35" s="4">
+        <f>$C35*N(H22)</f>
+        <v/>
+      </c>
+      <c r="I35" s="4">
+        <f>$C35*N(I22)</f>
+        <v/>
+      </c>
+      <c r="J35" s="4">
+        <f>$C35*N(J22)</f>
+        <v/>
+      </c>
+      <c r="K35" s="4">
+        <f>$C35*N(K22)</f>
+        <v/>
+      </c>
+      <c r="L35" s="4">
+        <f>$C35*N(L22)</f>
+        <v/>
+      </c>
+      <c r="M35" s="4">
+        <f>$C35*N(M22)</f>
+        <v/>
+      </c>
+      <c r="N35" s="4">
+        <f>$C35*N(N22)</f>
+        <v/>
+      </c>
+      <c r="O35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>PİSUVAR</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C36" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="4">
-        <f>$C35*N(D23)</f>
-        <v/>
-      </c>
-      <c r="E35" s="4">
-        <f>$C35*N(E23)</f>
-        <v/>
-      </c>
-      <c r="F35" s="4">
-        <f>$C35*N(F23)</f>
-        <v/>
-      </c>
-      <c r="G35" s="4">
-        <f>$C35*N(G23)</f>
-        <v/>
-      </c>
-      <c r="H35" s="4">
-        <f>$C35*N(H23)</f>
-        <v/>
-      </c>
-      <c r="I35" s="4">
-        <f>$C35*N(I23)</f>
-        <v/>
-      </c>
-      <c r="J35" s="4">
-        <f>$C35*N(J23)</f>
-        <v/>
-      </c>
-      <c r="K35" s="4">
-        <f>$C35*N(K23)</f>
-        <v/>
-      </c>
-      <c r="L35" s="4">
-        <f>$C35*N(L23)</f>
-        <v/>
-      </c>
-      <c r="M35" s="4">
-        <f>$C35*N(M23)</f>
-        <v/>
-      </c>
-      <c r="N35" s="4">
-        <f>$C35*N(N23)</f>
-        <v/>
-      </c>
-      <c r="O35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>TOPLAM</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="6">
-        <f>SUM(D28:D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="6">
-        <f>SUM(E28:E35)</f>
-        <v/>
-      </c>
-      <c r="F36" s="6">
-        <f>SUM(F28:F35)</f>
-        <v/>
-      </c>
-      <c r="G36" s="6">
-        <f>SUM(G28:G35)</f>
-        <v/>
-      </c>
-      <c r="H36" s="6">
-        <f>SUM(H28:H35)</f>
-        <v/>
-      </c>
-      <c r="I36" s="6">
-        <f>SUM(I28:I35)</f>
-        <v/>
-      </c>
-      <c r="J36" s="6">
-        <f>SUM(J28:J35)</f>
-        <v/>
-      </c>
-      <c r="K36" s="6">
-        <f>SUM(K28:K35)</f>
-        <v/>
-      </c>
-      <c r="L36" s="6">
-        <f>SUM(L28:L35)</f>
-        <v/>
-      </c>
-      <c r="M36" s="6">
-        <f>SUM(M28:M35)</f>
-        <v/>
-      </c>
-      <c r="N36" s="6">
-        <f>SUM(N28:N35)</f>
-        <v/>
-      </c>
-      <c r="O36" s="6">
-        <f>SUM(D36:N36)</f>
-        <v/>
-      </c>
+      <c r="D36" s="4">
+        <f>$C36*N(D23)</f>
+        <v/>
+      </c>
+      <c r="E36" s="4">
+        <f>$C36*N(E23)</f>
+        <v/>
+      </c>
+      <c r="F36" s="4">
+        <f>$C36*N(F23)</f>
+        <v/>
+      </c>
+      <c r="G36" s="4">
+        <f>$C36*N(G23)</f>
+        <v/>
+      </c>
+      <c r="H36" s="4">
+        <f>$C36*N(H23)</f>
+        <v/>
+      </c>
+      <c r="I36" s="4">
+        <f>$C36*N(I23)</f>
+        <v/>
+      </c>
+      <c r="J36" s="4">
+        <f>$C36*N(J23)</f>
+        <v/>
+      </c>
+      <c r="K36" s="4">
+        <f>$C36*N(K23)</f>
+        <v/>
+      </c>
+      <c r="L36" s="4">
+        <f>$C36*N(L23)</f>
+        <v/>
+      </c>
+      <c r="M36" s="4">
+        <f>$C36*N(M23)</f>
+        <v/>
+      </c>
+      <c r="N36" s="4">
+        <f>$C36*N(N23)</f>
+        <v/>
+      </c>
+      <c r="O36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>IZGARA (Ø100)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="4">
+        <f>$C37*N(D24)</f>
+        <v/>
+      </c>
+      <c r="E37" s="4">
+        <f>$C37*N(E24)</f>
+        <v/>
+      </c>
+      <c r="F37" s="4">
+        <f>$C37*N(F24)</f>
+        <v/>
+      </c>
+      <c r="G37" s="4">
+        <f>$C37*N(G24)</f>
+        <v/>
+      </c>
+      <c r="H37" s="4">
+        <f>$C37*N(H24)</f>
+        <v/>
+      </c>
+      <c r="I37" s="4">
+        <f>$C37*N(I24)</f>
+        <v/>
+      </c>
+      <c r="J37" s="4">
+        <f>$C37*N(J24)</f>
+        <v/>
+      </c>
+      <c r="K37" s="4">
+        <f>$C37*N(K24)</f>
+        <v/>
+      </c>
+      <c r="L37" s="4">
+        <f>$C37*N(L24)</f>
+        <v/>
+      </c>
+      <c r="M37" s="4">
+        <f>$C37*N(M24)</f>
+        <v/>
+      </c>
+      <c r="N37" s="4">
+        <f>$C37*N(N24)</f>
+        <v/>
+      </c>
+      <c r="O37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="6">
+        <f>SUM(D29:D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="6">
+        <f>SUM(E29:E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="6">
+        <f>SUM(F29:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="6">
+        <f>SUM(G29:G37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="6">
+        <f>SUM(H29:H37)</f>
+        <v/>
+      </c>
+      <c r="I38" s="6">
+        <f>SUM(I29:I37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="6">
+        <f>SUM(J29:J37)</f>
+        <v/>
+      </c>
+      <c r="K38" s="6">
+        <f>SUM(K29:K37)</f>
+        <v/>
+      </c>
+      <c r="L38" s="6">
+        <f>SUM(L29:L37)</f>
+        <v/>
+      </c>
+      <c r="M38" s="6">
+        <f>SUM(M29:M37)</f>
+        <v/>
+      </c>
+      <c r="N38" s="6">
+        <f>SUM(N29:N37)</f>
+        <v/>
+      </c>
+      <c r="O38" s="6">
+        <f>SUM(D38:N38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
           <t>Qww = 0,5 x √ΣSB (l/s)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4">
-        <f>ROUND(0.5*SQRT(D36),2)</f>
-        <v/>
-      </c>
-      <c r="E37" s="4">
-        <f>ROUND(0.5*SQRT(E36),2)</f>
-        <v/>
-      </c>
-      <c r="F37" s="4">
-        <f>ROUND(0.5*SQRT(F36),2)</f>
-        <v/>
-      </c>
-      <c r="G37" s="4">
-        <f>ROUND(0.5*SQRT(G36),2)</f>
-        <v/>
-      </c>
-      <c r="H37" s="4">
-        <f>ROUND(0.5*SQRT(H36),2)</f>
-        <v/>
-      </c>
-      <c r="I37" s="4">
-        <f>ROUND(0.5*SQRT(I36),2)</f>
-        <v/>
-      </c>
-      <c r="J37" s="4">
-        <f>ROUND(0.5*SQRT(J36),2)</f>
-        <v/>
-      </c>
-      <c r="K37" s="4">
-        <f>ROUND(0.5*SQRT(K36),2)</f>
-        <v/>
-      </c>
-      <c r="L37" s="4">
-        <f>ROUND(0.5*SQRT(L36),2)</f>
-        <v/>
-      </c>
-      <c r="M37" s="4">
-        <f>ROUND(0.5*SQRT(M36),2)</f>
-        <v/>
-      </c>
-      <c r="N37" s="4">
-        <f>ROUND(0.5*SQRT(N36),2)</f>
-        <v/>
-      </c>
-      <c r="O37" s="4" t="n"/>
-    </row>
-    <row r="40">
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4">
+        <f>ROUND(0.5*SQRT(D38),2)</f>
+        <v/>
+      </c>
+      <c r="E39" s="4">
+        <f>ROUND(0.5*SQRT(E38),2)</f>
+        <v/>
+      </c>
+      <c r="F39" s="4">
+        <f>ROUND(0.5*SQRT(F38),2)</f>
+        <v/>
+      </c>
+      <c r="G39" s="4">
+        <f>ROUND(0.5*SQRT(G38),2)</f>
+        <v/>
+      </c>
+      <c r="H39" s="4">
+        <f>ROUND(0.5*SQRT(H38),2)</f>
+        <v/>
+      </c>
+      <c r="I39" s="4">
+        <f>ROUND(0.5*SQRT(I38),2)</f>
+        <v/>
+      </c>
+      <c r="J39" s="4">
+        <f>ROUND(0.5*SQRT(J38),2)</f>
+        <v/>
+      </c>
+      <c r="K39" s="4">
+        <f>ROUND(0.5*SQRT(K38),2)</f>
+        <v/>
+      </c>
+      <c r="L39" s="4">
+        <f>ROUND(0.5*SQRT(L38),2)</f>
+        <v/>
+      </c>
+      <c r="M39" s="4">
+        <f>ROUND(0.5*SQRT(M38),2)</f>
+        <v/>
+      </c>
+      <c r="N39" s="4">
+        <f>ROUND(0.5*SQRT(N38),2)</f>
+        <v/>
+      </c>
+      <c r="O39" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>BORU ÇAPI</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>K.B.</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>YÜK DEĞERİ</t>
         </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="C43" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="C44" s="4" t="n">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>270</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="C45" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D45" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="D45" s="4" t="n">
-        <v>900</v>
-      </c>
       <c r="E45" s="4" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="C46" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D48" s="4" t="n">
         <v>2200</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E48" s="4" t="n">
         <v>1550</v>
       </c>
     </row>
@@ -3539,7 +3693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O46"/>
+  <dimension ref="B1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4174,187 +4328,157 @@
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="1" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>IZGARA (Ø100)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4">
+        <f>SUM(D24:N24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>PİS SU - KOLON YÜKLERİ (SB)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>CİNSİ</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>YÜK (SB)</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>SZ</t>
         </is>
-      </c>
-      <c r="O27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>KLOZET,HELA</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D28" s="4">
-        <f>$C28*N(D16)</f>
-        <v/>
-      </c>
-      <c r="E28" s="4">
-        <f>$C28*N(E16)</f>
-        <v/>
-      </c>
-      <c r="F28" s="4">
-        <f>$C28*N(F16)</f>
-        <v/>
-      </c>
-      <c r="G28" s="4">
-        <f>$C28*N(G16)</f>
-        <v/>
-      </c>
-      <c r="H28" s="4">
-        <f>$C28*N(H16)</f>
-        <v/>
-      </c>
-      <c r="I28" s="4">
-        <f>$C28*N(I16)</f>
-        <v/>
-      </c>
-      <c r="J28" s="4">
-        <f>$C28*N(J16)</f>
-        <v/>
-      </c>
-      <c r="K28" s="4">
-        <f>$C28*N(K16)</f>
-        <v/>
-      </c>
-      <c r="L28" s="4">
-        <f>$C28*N(L16)</f>
-        <v/>
-      </c>
-      <c r="M28" s="4">
-        <f>$C28*N(M16)</f>
-        <v/>
-      </c>
-      <c r="N28" s="4">
-        <f>$C28*N(N16)</f>
-        <v/>
       </c>
       <c r="O28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>BANYO KÜVETİ-DUŞ</t>
+          <t>KLOZET,HELA</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D29" s="4">
-        <f>$C29*N(D17)</f>
+        <f>$C29*N(D16)</f>
         <v/>
       </c>
       <c r="E29" s="4">
-        <f>$C29*N(E17)</f>
+        <f>$C29*N(E16)</f>
         <v/>
       </c>
       <c r="F29" s="4">
-        <f>$C29*N(F17)</f>
+        <f>$C29*N(F16)</f>
         <v/>
       </c>
       <c r="G29" s="4">
-        <f>$C29*N(G17)</f>
+        <f>$C29*N(G16)</f>
         <v/>
       </c>
       <c r="H29" s="4">
-        <f>$C29*N(H17)</f>
+        <f>$C29*N(H16)</f>
         <v/>
       </c>
       <c r="I29" s="4">
-        <f>$C29*N(I17)</f>
+        <f>$C29*N(I16)</f>
         <v/>
       </c>
       <c r="J29" s="4">
-        <f>$C29*N(J17)</f>
+        <f>$C29*N(J16)</f>
         <v/>
       </c>
       <c r="K29" s="4">
-        <f>$C29*N(K17)</f>
+        <f>$C29*N(K16)</f>
         <v/>
       </c>
       <c r="L29" s="4">
-        <f>$C29*N(L17)</f>
+        <f>$C29*N(L16)</f>
         <v/>
       </c>
       <c r="M29" s="4">
-        <f>$C29*N(M17)</f>
+        <f>$C29*N(M16)</f>
         <v/>
       </c>
       <c r="N29" s="4">
-        <f>$C29*N(N17)</f>
+        <f>$C29*N(N16)</f>
         <v/>
       </c>
       <c r="O29" s="4" t="n"/>
@@ -4362,54 +4486,54 @@
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>SİFON,EVİYE</t>
+          <t>BANYO KÜVETİ-DUŞ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D30" s="4">
-        <f>$C30*N(D18)</f>
+        <f>$C30*N(D17)</f>
         <v/>
       </c>
       <c r="E30" s="4">
-        <f>$C30*N(E18)</f>
+        <f>$C30*N(E17)</f>
         <v/>
       </c>
       <c r="F30" s="4">
-        <f>$C30*N(F18)</f>
+        <f>$C30*N(F17)</f>
         <v/>
       </c>
       <c r="G30" s="4">
-        <f>$C30*N(G18)</f>
+        <f>$C30*N(G17)</f>
         <v/>
       </c>
       <c r="H30" s="4">
-        <f>$C30*N(H18)</f>
+        <f>$C30*N(H17)</f>
         <v/>
       </c>
       <c r="I30" s="4">
-        <f>$C30*N(I18)</f>
+        <f>$C30*N(I17)</f>
         <v/>
       </c>
       <c r="J30" s="4">
-        <f>$C30*N(J18)</f>
+        <f>$C30*N(J17)</f>
         <v/>
       </c>
       <c r="K30" s="4">
-        <f>$C30*N(K18)</f>
+        <f>$C30*N(K17)</f>
         <v/>
       </c>
       <c r="L30" s="4">
-        <f>$C30*N(L18)</f>
+        <f>$C30*N(L17)</f>
         <v/>
       </c>
       <c r="M30" s="4">
-        <f>$C30*N(M18)</f>
+        <f>$C30*N(M17)</f>
         <v/>
       </c>
       <c r="N30" s="4">
-        <f>$C30*N(N18)</f>
+        <f>$C30*N(N17)</f>
         <v/>
       </c>
       <c r="O30" s="4" t="n"/>
@@ -4417,54 +4541,54 @@
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>İKİ GÖZLÜ EVİYE</t>
+          <t>SİFON,EVİYE</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D31" s="4">
-        <f>$C31*N(D19)</f>
+        <f>$C31*N(D18)</f>
         <v/>
       </c>
       <c r="E31" s="4">
-        <f>$C31*N(E19)</f>
+        <f>$C31*N(E18)</f>
         <v/>
       </c>
       <c r="F31" s="4">
-        <f>$C31*N(F19)</f>
+        <f>$C31*N(F18)</f>
         <v/>
       </c>
       <c r="G31" s="4">
-        <f>$C31*N(G19)</f>
+        <f>$C31*N(G18)</f>
         <v/>
       </c>
       <c r="H31" s="4">
-        <f>$C31*N(H19)</f>
+        <f>$C31*N(H18)</f>
         <v/>
       </c>
       <c r="I31" s="4">
-        <f>$C31*N(I19)</f>
+        <f>$C31*N(I18)</f>
         <v/>
       </c>
       <c r="J31" s="4">
-        <f>$C31*N(J19)</f>
+        <f>$C31*N(J18)</f>
         <v/>
       </c>
       <c r="K31" s="4">
-        <f>$C31*N(K19)</f>
+        <f>$C31*N(K18)</f>
         <v/>
       </c>
       <c r="L31" s="4">
-        <f>$C31*N(L19)</f>
+        <f>$C31*N(L18)</f>
         <v/>
       </c>
       <c r="M31" s="4">
-        <f>$C31*N(M19)</f>
+        <f>$C31*N(M18)</f>
         <v/>
       </c>
       <c r="N31" s="4">
-        <f>$C31*N(N19)</f>
+        <f>$C31*N(N18)</f>
         <v/>
       </c>
       <c r="O31" s="4" t="n"/>
@@ -4472,54 +4596,54 @@
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>LAVABO</t>
+          <t>İKİ GÖZLÜ EVİYE</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D32" s="4">
-        <f>$C32*N(D20)</f>
+        <f>$C32*N(D19)</f>
         <v/>
       </c>
       <c r="E32" s="4">
-        <f>$C32*N(E20)</f>
+        <f>$C32*N(E19)</f>
         <v/>
       </c>
       <c r="F32" s="4">
-        <f>$C32*N(F20)</f>
+        <f>$C32*N(F19)</f>
         <v/>
       </c>
       <c r="G32" s="4">
-        <f>$C32*N(G20)</f>
+        <f>$C32*N(G19)</f>
         <v/>
       </c>
       <c r="H32" s="4">
-        <f>$C32*N(H20)</f>
+        <f>$C32*N(H19)</f>
         <v/>
       </c>
       <c r="I32" s="4">
-        <f>$C32*N(I20)</f>
+        <f>$C32*N(I19)</f>
         <v/>
       </c>
       <c r="J32" s="4">
-        <f>$C32*N(J20)</f>
+        <f>$C32*N(J19)</f>
         <v/>
       </c>
       <c r="K32" s="4">
-        <f>$C32*N(K20)</f>
+        <f>$C32*N(K19)</f>
         <v/>
       </c>
       <c r="L32" s="4">
-        <f>$C32*N(L20)</f>
+        <f>$C32*N(L19)</f>
         <v/>
       </c>
       <c r="M32" s="4">
-        <f>$C32*N(M20)</f>
+        <f>$C32*N(M19)</f>
         <v/>
       </c>
       <c r="N32" s="4">
-        <f>$C32*N(N20)</f>
+        <f>$C32*N(N19)</f>
         <v/>
       </c>
       <c r="O32" s="4" t="n"/>
@@ -4527,54 +4651,54 @@
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>YERSÜZGECİ</t>
+          <t>LAVABO</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="4">
-        <f>$C33*N(D21)</f>
+        <f>$C33*N(D20)</f>
         <v/>
       </c>
       <c r="E33" s="4">
-        <f>$C33*N(E21)</f>
+        <f>$C33*N(E20)</f>
         <v/>
       </c>
       <c r="F33" s="4">
-        <f>$C33*N(F21)</f>
+        <f>$C33*N(F20)</f>
         <v/>
       </c>
       <c r="G33" s="4">
-        <f>$C33*N(G21)</f>
+        <f>$C33*N(G20)</f>
         <v/>
       </c>
       <c r="H33" s="4">
-        <f>$C33*N(H21)</f>
+        <f>$C33*N(H20)</f>
         <v/>
       </c>
       <c r="I33" s="4">
-        <f>$C33*N(I21)</f>
+        <f>$C33*N(I20)</f>
         <v/>
       </c>
       <c r="J33" s="4">
-        <f>$C33*N(J21)</f>
+        <f>$C33*N(J20)</f>
         <v/>
       </c>
       <c r="K33" s="4">
-        <f>$C33*N(K21)</f>
+        <f>$C33*N(K20)</f>
         <v/>
       </c>
       <c r="L33" s="4">
-        <f>$C33*N(L21)</f>
+        <f>$C33*N(L20)</f>
         <v/>
       </c>
       <c r="M33" s="4">
-        <f>$C33*N(M21)</f>
+        <f>$C33*N(M20)</f>
         <v/>
       </c>
       <c r="N33" s="4">
-        <f>$C33*N(N21)</f>
+        <f>$C33*N(N20)</f>
         <v/>
       </c>
       <c r="O33" s="4" t="n"/>
@@ -4582,54 +4706,54 @@
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ÇAMAŞIR,BUL.MAK</t>
+          <t>YERSÜZGECİ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34" s="4">
-        <f>$C34*N(D22)</f>
+        <f>$C34*N(D21)</f>
         <v/>
       </c>
       <c r="E34" s="4">
-        <f>$C34*N(E22)</f>
+        <f>$C34*N(E21)</f>
         <v/>
       </c>
       <c r="F34" s="4">
-        <f>$C34*N(F22)</f>
+        <f>$C34*N(F21)</f>
         <v/>
       </c>
       <c r="G34" s="4">
-        <f>$C34*N(G22)</f>
+        <f>$C34*N(G21)</f>
         <v/>
       </c>
       <c r="H34" s="4">
-        <f>$C34*N(H22)</f>
+        <f>$C34*N(H21)</f>
         <v/>
       </c>
       <c r="I34" s="4">
-        <f>$C34*N(I22)</f>
+        <f>$C34*N(I21)</f>
         <v/>
       </c>
       <c r="J34" s="4">
-        <f>$C34*N(J22)</f>
+        <f>$C34*N(J21)</f>
         <v/>
       </c>
       <c r="K34" s="4">
-        <f>$C34*N(K22)</f>
+        <f>$C34*N(K21)</f>
         <v/>
       </c>
       <c r="L34" s="4">
-        <f>$C34*N(L22)</f>
+        <f>$C34*N(L21)</f>
         <v/>
       </c>
       <c r="M34" s="4">
-        <f>$C34*N(M22)</f>
+        <f>$C34*N(M21)</f>
         <v/>
       </c>
       <c r="N34" s="4">
-        <f>$C34*N(N22)</f>
+        <f>$C34*N(N21)</f>
         <v/>
       </c>
       <c r="O34" s="4" t="n"/>
@@ -4637,247 +4761,357 @@
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>ÇAMAŞIR,BUL.MAK</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="4">
+        <f>$C35*N(D22)</f>
+        <v/>
+      </c>
+      <c r="E35" s="4">
+        <f>$C35*N(E22)</f>
+        <v/>
+      </c>
+      <c r="F35" s="4">
+        <f>$C35*N(F22)</f>
+        <v/>
+      </c>
+      <c r="G35" s="4">
+        <f>$C35*N(G22)</f>
+        <v/>
+      </c>
+      <c r="H35" s="4">
+        <f>$C35*N(H22)</f>
+        <v/>
+      </c>
+      <c r="I35" s="4">
+        <f>$C35*N(I22)</f>
+        <v/>
+      </c>
+      <c r="J35" s="4">
+        <f>$C35*N(J22)</f>
+        <v/>
+      </c>
+      <c r="K35" s="4">
+        <f>$C35*N(K22)</f>
+        <v/>
+      </c>
+      <c r="L35" s="4">
+        <f>$C35*N(L22)</f>
+        <v/>
+      </c>
+      <c r="M35" s="4">
+        <f>$C35*N(M22)</f>
+        <v/>
+      </c>
+      <c r="N35" s="4">
+        <f>$C35*N(N22)</f>
+        <v/>
+      </c>
+      <c r="O35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>PİSUVAR</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C36" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="4">
-        <f>$C35*N(D23)</f>
-        <v/>
-      </c>
-      <c r="E35" s="4">
-        <f>$C35*N(E23)</f>
-        <v/>
-      </c>
-      <c r="F35" s="4">
-        <f>$C35*N(F23)</f>
-        <v/>
-      </c>
-      <c r="G35" s="4">
-        <f>$C35*N(G23)</f>
-        <v/>
-      </c>
-      <c r="H35" s="4">
-        <f>$C35*N(H23)</f>
-        <v/>
-      </c>
-      <c r="I35" s="4">
-        <f>$C35*N(I23)</f>
-        <v/>
-      </c>
-      <c r="J35" s="4">
-        <f>$C35*N(J23)</f>
-        <v/>
-      </c>
-      <c r="K35" s="4">
-        <f>$C35*N(K23)</f>
-        <v/>
-      </c>
-      <c r="L35" s="4">
-        <f>$C35*N(L23)</f>
-        <v/>
-      </c>
-      <c r="M35" s="4">
-        <f>$C35*N(M23)</f>
-        <v/>
-      </c>
-      <c r="N35" s="4">
-        <f>$C35*N(N23)</f>
-        <v/>
-      </c>
-      <c r="O35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>TOPLAM</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="6">
-        <f>SUM(D28:D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="6">
-        <f>SUM(E28:E35)</f>
-        <v/>
-      </c>
-      <c r="F36" s="6">
-        <f>SUM(F28:F35)</f>
-        <v/>
-      </c>
-      <c r="G36" s="6">
-        <f>SUM(G28:G35)</f>
-        <v/>
-      </c>
-      <c r="H36" s="6">
-        <f>SUM(H28:H35)</f>
-        <v/>
-      </c>
-      <c r="I36" s="6">
-        <f>SUM(I28:I35)</f>
-        <v/>
-      </c>
-      <c r="J36" s="6">
-        <f>SUM(J28:J35)</f>
-        <v/>
-      </c>
-      <c r="K36" s="6">
-        <f>SUM(K28:K35)</f>
-        <v/>
-      </c>
-      <c r="L36" s="6">
-        <f>SUM(L28:L35)</f>
-        <v/>
-      </c>
-      <c r="M36" s="6">
-        <f>SUM(M28:M35)</f>
-        <v/>
-      </c>
-      <c r="N36" s="6">
-        <f>SUM(N28:N35)</f>
-        <v/>
-      </c>
-      <c r="O36" s="6">
-        <f>SUM(D36:N36)</f>
-        <v/>
-      </c>
+      <c r="D36" s="4">
+        <f>$C36*N(D23)</f>
+        <v/>
+      </c>
+      <c r="E36" s="4">
+        <f>$C36*N(E23)</f>
+        <v/>
+      </c>
+      <c r="F36" s="4">
+        <f>$C36*N(F23)</f>
+        <v/>
+      </c>
+      <c r="G36" s="4">
+        <f>$C36*N(G23)</f>
+        <v/>
+      </c>
+      <c r="H36" s="4">
+        <f>$C36*N(H23)</f>
+        <v/>
+      </c>
+      <c r="I36" s="4">
+        <f>$C36*N(I23)</f>
+        <v/>
+      </c>
+      <c r="J36" s="4">
+        <f>$C36*N(J23)</f>
+        <v/>
+      </c>
+      <c r="K36" s="4">
+        <f>$C36*N(K23)</f>
+        <v/>
+      </c>
+      <c r="L36" s="4">
+        <f>$C36*N(L23)</f>
+        <v/>
+      </c>
+      <c r="M36" s="4">
+        <f>$C36*N(M23)</f>
+        <v/>
+      </c>
+      <c r="N36" s="4">
+        <f>$C36*N(N23)</f>
+        <v/>
+      </c>
+      <c r="O36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>IZGARA (Ø100)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="4">
+        <f>$C37*N(D24)</f>
+        <v/>
+      </c>
+      <c r="E37" s="4">
+        <f>$C37*N(E24)</f>
+        <v/>
+      </c>
+      <c r="F37" s="4">
+        <f>$C37*N(F24)</f>
+        <v/>
+      </c>
+      <c r="G37" s="4">
+        <f>$C37*N(G24)</f>
+        <v/>
+      </c>
+      <c r="H37" s="4">
+        <f>$C37*N(H24)</f>
+        <v/>
+      </c>
+      <c r="I37" s="4">
+        <f>$C37*N(I24)</f>
+        <v/>
+      </c>
+      <c r="J37" s="4">
+        <f>$C37*N(J24)</f>
+        <v/>
+      </c>
+      <c r="K37" s="4">
+        <f>$C37*N(K24)</f>
+        <v/>
+      </c>
+      <c r="L37" s="4">
+        <f>$C37*N(L24)</f>
+        <v/>
+      </c>
+      <c r="M37" s="4">
+        <f>$C37*N(M24)</f>
+        <v/>
+      </c>
+      <c r="N37" s="4">
+        <f>$C37*N(N24)</f>
+        <v/>
+      </c>
+      <c r="O37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="6">
+        <f>SUM(D29:D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="6">
+        <f>SUM(E29:E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="6">
+        <f>SUM(F29:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="6">
+        <f>SUM(G29:G37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="6">
+        <f>SUM(H29:H37)</f>
+        <v/>
+      </c>
+      <c r="I38" s="6">
+        <f>SUM(I29:I37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="6">
+        <f>SUM(J29:J37)</f>
+        <v/>
+      </c>
+      <c r="K38" s="6">
+        <f>SUM(K29:K37)</f>
+        <v/>
+      </c>
+      <c r="L38" s="6">
+        <f>SUM(L29:L37)</f>
+        <v/>
+      </c>
+      <c r="M38" s="6">
+        <f>SUM(M29:M37)</f>
+        <v/>
+      </c>
+      <c r="N38" s="6">
+        <f>SUM(N29:N37)</f>
+        <v/>
+      </c>
+      <c r="O38" s="6">
+        <f>SUM(D38:N38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
           <t>Qww = 0,5 x √ΣSB (l/s)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4">
-        <f>ROUND(0.5*SQRT(D36),2)</f>
-        <v/>
-      </c>
-      <c r="E37" s="4">
-        <f>ROUND(0.5*SQRT(E36),2)</f>
-        <v/>
-      </c>
-      <c r="F37" s="4">
-        <f>ROUND(0.5*SQRT(F36),2)</f>
-        <v/>
-      </c>
-      <c r="G37" s="4">
-        <f>ROUND(0.5*SQRT(G36),2)</f>
-        <v/>
-      </c>
-      <c r="H37" s="4">
-        <f>ROUND(0.5*SQRT(H36),2)</f>
-        <v/>
-      </c>
-      <c r="I37" s="4">
-        <f>ROUND(0.5*SQRT(I36),2)</f>
-        <v/>
-      </c>
-      <c r="J37" s="4">
-        <f>ROUND(0.5*SQRT(J36),2)</f>
-        <v/>
-      </c>
-      <c r="K37" s="4">
-        <f>ROUND(0.5*SQRT(K36),2)</f>
-        <v/>
-      </c>
-      <c r="L37" s="4">
-        <f>ROUND(0.5*SQRT(L36),2)</f>
-        <v/>
-      </c>
-      <c r="M37" s="4">
-        <f>ROUND(0.5*SQRT(M36),2)</f>
-        <v/>
-      </c>
-      <c r="N37" s="4">
-        <f>ROUND(0.5*SQRT(N36),2)</f>
-        <v/>
-      </c>
-      <c r="O37" s="4" t="n"/>
-    </row>
-    <row r="40">
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4">
+        <f>ROUND(0.5*SQRT(D38),2)</f>
+        <v/>
+      </c>
+      <c r="E39" s="4">
+        <f>ROUND(0.5*SQRT(E38),2)</f>
+        <v/>
+      </c>
+      <c r="F39" s="4">
+        <f>ROUND(0.5*SQRT(F38),2)</f>
+        <v/>
+      </c>
+      <c r="G39" s="4">
+        <f>ROUND(0.5*SQRT(G38),2)</f>
+        <v/>
+      </c>
+      <c r="H39" s="4">
+        <f>ROUND(0.5*SQRT(H38),2)</f>
+        <v/>
+      </c>
+      <c r="I39" s="4">
+        <f>ROUND(0.5*SQRT(I38),2)</f>
+        <v/>
+      </c>
+      <c r="J39" s="4">
+        <f>ROUND(0.5*SQRT(J38),2)</f>
+        <v/>
+      </c>
+      <c r="K39" s="4">
+        <f>ROUND(0.5*SQRT(K38),2)</f>
+        <v/>
+      </c>
+      <c r="L39" s="4">
+        <f>ROUND(0.5*SQRT(L38),2)</f>
+        <v/>
+      </c>
+      <c r="M39" s="4">
+        <f>ROUND(0.5*SQRT(M38),2)</f>
+        <v/>
+      </c>
+      <c r="N39" s="4">
+        <f>ROUND(0.5*SQRT(N38),2)</f>
+        <v/>
+      </c>
+      <c r="O39" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>BORU ÇAPI</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>K.B.</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>YÜK DEĞERİ</t>
         </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="C43" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="C44" s="4" t="n">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>270</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="C45" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D45" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="D45" s="4" t="n">
-        <v>900</v>
-      </c>
       <c r="E45" s="4" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="C46" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D48" s="4" t="n">
         <v>2200</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E48" s="4" t="n">
         <v>1550</v>
       </c>
     </row>
@@ -4892,315 +5126,611 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>CİHAZ KULLANMA YERİ</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>AKMA BASINCI</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>DEBİ</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>YÜK BİRİMİ</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>PİS SU POMPASI HESAPLARI (TS EN 12056-2 / -4) - HER ÇUKUR İÇİN AYRI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>l / s</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>YB</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Musluk veya boşalma vanası DN 15 mm</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>49035</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.5</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Qww = K x √ΣSB  (K = 0,5 konut) ;  Hm = Hgeo + sürtünme (Hazen-Williams, C=140) + özel kayıplar ;  Vaktif ≥ Qp / (4 x Z)</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Musluk veya boşalma vanası DN 20 mm</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>49035</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>HESAP ADIMI</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>PİS SU ÇUKURU-1 (B1 BLOK)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>PİS SU ÇUKURU-2 (B2 BLOK)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PİS SU ÇUKURU-3 (B3 BLOK)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>BİRİM</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Musluk veya boşalma vanası DN 25 mm</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>49035</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>36</v>
-      </c>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Toplandığı yer</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Bodrum: 5 yer süzgeci + 1 ızgara</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Bodrum birimi (P9+P10) + 7 süzgeç</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Bodrum birimi (P9+P10) + 7 süzgeç</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Lavabo</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>49035</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.5</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Toplam su birimi ΣSB</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Küvetli banyo DN 15 mm</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>98070</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.5</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Atık su debisi Qww = 0,5√ΣSB</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>l/s</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Küvetli banyo DN 20 mm</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>98070</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>16</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Atık su debisi</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>m³/h</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Pisuvar</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>49035</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Basma hattı çapı</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>DN50</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>DN50</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>DN50</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Hela rezervuarı</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>49035</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.25</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Basma hattında hız (Qww)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Basınçlı hela yıkayıcısı DN 15 mm</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>127491</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6</v>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Geometrik yükseklik Hgeo = çukur derinliği + bodrum kat yük. - 0,40</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>3,45</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>3,45</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>3,45</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>mSS</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Basınçlı hela yıkayıcısı DN 20 mm</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>117684</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D12" t="n">
-        <v>11</v>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Basma hattı uzunluğu (kabul)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Basınçlı hela yıkayıcısı DN 25 mm</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>39228</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>27</v>
-      </c>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Özel kayıp katsayısı Σζ (çek valf+vana+3 dirsek+çıkış)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>5,3</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>5,3</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>5,3</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Şofben ( 10 l/dak'yatak kadar)</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>245175</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.5</v>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Gerekli basma yüksekliği Hm (Qww)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>mSS</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Şofben ( 16 l/dak'yatak kadar)</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>245175</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Hm x 1,10 emniyet</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>mSS</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Şofben ( 26 l/dak'yatak kadar)</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>245175</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Şemadaki pompa: 13.7 m³/h - 5.2 mSS (1 asıl + 1 yedek)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Termosifon</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>49035</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.5</v>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Sistem direnci 13.7 m³/h debide</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>mSS</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Çamaşır, bulaşık makinası</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>49035</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.5</v>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Basma hattında hız (13.7 m³/h)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1 mSS = 9807 Pa</t>
-        </is>
-      </c>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Pompa debisi ≥ Qww</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>UYGUNDUR</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>YETERSİZ (≥14.4 m³/h)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>YETERSİZ (≥14.4 m³/h)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ÇİZELGE_1</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Pompa basma yük. ≥ sistem direnci</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>YETERSİZ (≥5.7 mSS)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>YETERSİZ (≥5.7 mSS)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>YETERSİZ (≥5.7 mSS)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Çukur ölçüsü (şemadaki) 70x70x85 cm - aktif hacim (min. seviye 0.30 m, pay 0.10 m)</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Gerekli aktif hacim Qp/(4·Z), Z = 15 kalkış/saat</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Çukur hacmi</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>YETERSİZ</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>YETERSİZ</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>YETERSİZ</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>ÖNERİLEN POMPA DEBİSİ</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>m³/h</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>ÖNERİLEN POMPA BASMA YÜKSEKLİĞİ (x1,10, DN50 basma)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>mSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>ÖNERİLEN ÇUKUR ÖLÇÜSÜ</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>70x70x85</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>80x80x100</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>80x80x100</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Önerilen çukur aktif hacmi / gerekli</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>0.22 / 0.17</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>0.38 / 0.25</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>0.38 / 0.25</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Motor gücü P = ρ·g·Q·H/η (η = 0,40) → seçilecek motor</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>0.37 → 0.55 kW</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>0.72 → 1.1 kW</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>0.72 → 1.1 kW</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>*Pompalar dalgıç-parçalayıcı tip, 1 asıl + 1 yedek, seviye şamandıralı otomatik çalışmalı ve yüksek seviye alarmlı olacaktır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>*Basma hattı kanal geri tepmesine karşı çek valfli ve en yüksek kanal seviyesinin üstünden (geri tepme döngüsü) bağlanacaktır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>*Basma hattı uzunluğu şema ölçeksiz olduğundan 15 m kabul edilmiştir; uygulamada boy farklıysa Hm yeniden kontrol edilmelidir.</t>
         </is>
       </c>
     </row>
@@ -5215,576 +5745,271 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M15"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sayacın Anma                             Çapı        mm DN  </t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Sayacın su kapasitesi</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sayaçtaki Basınç Kaybı(Pa)                                           İDEAL SAYAÇLAR</t>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>KULLANMA SUYU DEPOSU VE HİDROFOR KONTROLÜ</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>m3 /h</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>9807</v>
-      </c>
-      <c r="E3" t="n">
-        <v>19641</v>
-      </c>
-      <c r="F3" t="n">
-        <v>29421</v>
-      </c>
-      <c r="G3" t="n">
-        <v>39228</v>
-      </c>
-      <c r="H3" t="n">
-        <v>49035</v>
-      </c>
-      <c r="I3" t="n">
-        <v>58842</v>
-      </c>
-      <c r="J3" t="n">
-        <v>68649</v>
-      </c>
-      <c r="K3" t="n">
-        <v>78456</v>
-      </c>
-      <c r="L3" t="n">
-        <v>88263</v>
-      </c>
-      <c r="M3" t="n">
-        <v>98070</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>HESAP ADIMI</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>DEĞER</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BİRİM</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>debi ( l/s)</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.646</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.833</v>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Bağımsız birim (daire) sayısı - şemadaki şofben adedi</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>38 (B1 12, B2 13, B3 13)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Yük birimi (YB)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>(1.1)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(2.2)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>(3.3)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>(4.4)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(5.6)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>(6.7)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>(7.8)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>(7.9)</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>(10.0)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>(11.1)</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Kişi sayısı (daire başına 4 kişi)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>kişi</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>debi ( l/s)</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.878</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.076</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.162</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.242</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.318</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.389</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Günlük su ihtiyacı (100 l/kişi·gün)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>m³/gün</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Yük birimi (YB)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>(3.1)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>(6.2)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>(9.3.)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>(13.3)</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(15.4)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>(18.5)</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>(21.6)</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>(22.1)</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>(27.8)</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>(30.9)</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Seçilen depo hacmi</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>m³</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>32</v>
-      </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>debi ( l/s)</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.055</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.506</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.627</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.739</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.845</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.944</v>
-      </c>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Depo kontrolü</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>UYGUNDUR</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Yük birimi (YB)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>(6.0)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>(12.1)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>(18.1)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>(24.2)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(30.3)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>(36.3)</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>(42.3)</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>(48.4)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>(54.4)</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>(60.5)</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Toplam yük birimi ΣYB (şema)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>540</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>YB</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>40</v>
-      </c>
-      <c r="B10" t="n">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Anlık debi Q = 0,25√ΣYB</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>l/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Anlık debi</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>m³/h</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Statik yükseklik (bina yüksekliği)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>mSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Kritik devre boru kayıpları</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>mSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Akma basıncı + sayaç kaybı</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>debi ( l/s)</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.878</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.242</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.521</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.757</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.964</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.152</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.324</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.485</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2.635</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2.778</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Yük birimi (YB)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>(12.3)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(24.7)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>(37.0)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>(49.4)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(61.7)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>(74.1)</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>(86.4)</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>(98.8)</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>(111.1)</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>(123.5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>50</v>
-      </c>
-      <c r="B12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>debi ( l/s)</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1.757</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.484</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3.513</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3.514</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.928</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4.303</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.648</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.969</v>
-      </c>
-      <c r="L12" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="M12" t="n">
-        <v>5.556</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Yük birimi (YB)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>(49.4)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>(98.8)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>(197.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>(264.9)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(294.3)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>(345.7)</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>(395.7)</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>(395.1)</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>(444.4)</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>(493.8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1 mSS = 9807 Pa = 9,807 kPa</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>mSS</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ÇİZELGE_2</t>
-        </is>
-      </c>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Hidrofor kollektörü / emme kayıpları (kabul)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>mSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Gerekli hidrofor basma yüksekliği (alt çalışma basıncı)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>mSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Şemadaki hidrofor</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>9,75 m³/h - 67,10 mSS</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Basma yüksekliği kontrolü</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>UYGUNDUR</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Debi kontrolü (anlık debiye göre)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>YETERSİZ (≥20.9 m³/h)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5797,6 +6022,911 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CİHAZ KULLANMA YERİ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AKMA BASINCI</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DEBİ</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>YÜK BİRİMİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>l / s</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>YB</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Musluk veya boşalma vanası DN 15 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>49035</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Musluk veya boşalma vanası DN 20 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>49035</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Musluk veya boşalma vanası DN 25 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>49035</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lavabo</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>49035</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Küvetli banyo DN 15 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>98070</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Küvetli banyo DN 20 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>98070</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pisuvar</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>49035</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Hela rezervuarı</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>49035</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Basınçlı hela yıkayıcısı DN 15 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>127491</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Basınçlı hela yıkayıcısı DN 20 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>117684</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Basınçlı hela yıkayıcısı DN 25 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>39228</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Şofben ( 10 l/dak'yatak kadar)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>245175</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Şofben ( 16 l/dak'yatak kadar)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>245175</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Şofben ( 26 l/dak'yatak kadar)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>245175</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Termosifon</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>49035</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Çamaşır, bulaşık makinası</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>49035</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1 mSS = 9807 Pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ÇİZELGE_1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:M15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sayacın Anma                             Çapı        mm DN  </t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sayacın su kapasitesi</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sayaçtaki Basınç Kaybı(Pa)                                           İDEAL SAYAÇLAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>m3 /h</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9807</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19641</v>
+      </c>
+      <c r="F3" t="n">
+        <v>29421</v>
+      </c>
+      <c r="G3" t="n">
+        <v>39228</v>
+      </c>
+      <c r="H3" t="n">
+        <v>49035</v>
+      </c>
+      <c r="I3" t="n">
+        <v>58842</v>
+      </c>
+      <c r="J3" t="n">
+        <v>68649</v>
+      </c>
+      <c r="K3" t="n">
+        <v>78456</v>
+      </c>
+      <c r="L3" t="n">
+        <v>88263</v>
+      </c>
+      <c r="M3" t="n">
+        <v>98070</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>debi ( l/s)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.833</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Yük birimi (YB)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>(1.1)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(2.2)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(3.3)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>(4.4)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(5.6)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>(6.7)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>(7.8)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>(7.9)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>(10.0)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>(11.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>debi ( l/s)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.389</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yük birimi (YB)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>(3.1)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(6.2)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>(9.3.)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>(13.3)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(15.4)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>(18.5)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>(21.6)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>(22.1)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>(27.8)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>(30.9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>debi ( l/s)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.627</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.739</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.944</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yük birimi (YB)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(6.0)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(12.1)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>(18.1)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>(24.2)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(30.3)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>(36.3)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>(42.3)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>(48.4)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>(54.4)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>(60.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>40</v>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>debi ( l/s)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.521</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.757</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.964</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.152</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.324</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.778</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Yük birimi (YB)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(12.3)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(24.7)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>(37.0)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>(49.4)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(61.7)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>(74.1)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>(86.4)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>(98.8)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>(111.1)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>(123.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>50</v>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>debi ( l/s)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.757</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.514</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.928</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.303</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.648</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.969</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.556</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yük birimi (YB)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>(49.4)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(98.8)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>(197.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>(264.9)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(294.3)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>(345.7)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>(395.7)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>(395.1)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>(444.4)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>(493.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1 mSS = 9807 Pa = 9,807 kPa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ÇİZELGE_2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B1:AB71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/proje/hesaplar_sema/HESAPLAR_SIHHI.xlsx
+++ b/proje/hesaplar_sema/HESAPLAR_SIHHI.xlsx
@@ -9748,7 +9748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9945,13 +9945,6 @@
         <v/>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>*Yağmur suyu pis su kanalına bağlanmayacak, yağmur suyu kanalına (rögarına) verilecektir.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
